--- a/Data/joueur_medias.xlsx
+++ b/Data/joueur_medias.xlsx
@@ -31,16 +31,13 @@
     <x:t>DateAjout</x:t>
   </x:si>
   <x:si>
-    <x:t>/uploads/joueurs/2/2a9a66d7-5102-4f6e-baa5-4729400d329a.jpg</x:t>
+    <x:t>/uploads/joueurs/1/1bb82546-1eec-45d8-bf11-dcc152fd2c08.JPG</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>/uploads/joueurs/2/39e127e5-5ee3-4204-b2d2-02e62ac7fde3.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/joueurs/12/49916ddf-5450-4564-a521-faaa2ecb35c2.jpg</x:t>
+    <x:t>/uploads/joueurs/1/8d6898f4-4e30-4bdc-a440-9ccd8763c904.JPG</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -423,7 +420,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
         <x:v>5</x:v>
@@ -432,7 +429,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E2" s="1">
-        <x:v>46111.1300491898</x:v>
+        <x:v>46118.6625094213</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -440,7 +437,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
         <x:v>7</x:v>
@@ -449,24 +446,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E3" s="1">
-        <x:v>46111.1302375579</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:5">
-      <x:c r="A4" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B4" s="0">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E4" s="1">
-        <x:v>46111.9751089931</x:v>
+        <x:v>46118.6626576157</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/joueur_medias.xlsx
+++ b/Data/joueur_medias.xlsx
@@ -31,13 +31,19 @@
     <x:t>DateAjout</x:t>
   </x:si>
   <x:si>
-    <x:t>/uploads/joueurs/1/1bb82546-1eec-45d8-bf11-dcc152fd2c08.JPG</x:t>
+    <x:t>/uploads/joueurs/979a392c-a4f5-456f-8b74-0d8d2a77a54a.png</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>/uploads/joueurs/1/8d6898f4-4e30-4bdc-a440-9ccd8763c904.JPG</x:t>
+    <x:t>/uploads/joueurs/0fa26f9e-7baa-46c2-b5b3-f12b064cfff6.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/joueurs/80acbdc0-1290-4d34-b1c2-8d771d96a4c0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/joueurs/6cf7a605-cb43-4d7a-a29b-1b01835b4c90.JPG</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -429,7 +435,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E2" s="1">
-        <x:v>46118.6625094213</x:v>
+        <x:v>46124.8674214931</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -446,7 +452,41 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E3" s="1">
-        <x:v>46118.6626576157</x:v>
+        <x:v>46124.8678176736</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:5">
+      <x:c r="A4" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E4" s="1">
+        <x:v>46124.8847539468</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:5">
+      <x:c r="A5" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E5" s="1">
+        <x:v>46126.03142625</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/joueur_medias.xlsx
+++ b/Data/joueur_medias.xlsx
@@ -29,21 +29,6 @@
   </x:si>
   <x:si>
     <x:t>DateAjout</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/joueurs/979a392c-a4f5-456f-8b74-0d8d2a77a54a.png</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/joueurs/0fa26f9e-7baa-46c2-b5b3-f12b064cfff6.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/joueurs/80acbdc0-1290-4d34-b1c2-8d771d96a4c0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/joueurs/6cf7a605-cb43-4d7a-a29b-1b01835b4c90.JPG</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -89,20 +74,13 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="2">
+  <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="2">
+  <x:cellXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -421,74 +399,6 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:5">
-      <x:c r="A2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E2" s="1">
-        <x:v>46124.8674214931</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:5">
-      <x:c r="A3" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E3" s="1">
-        <x:v>46124.8678176736</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:5">
-      <x:c r="A4" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B4" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E4" s="1">
-        <x:v>46124.8847539468</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:5">
-      <x:c r="A5" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B5" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E5" s="1">
-        <x:v>46126.03142625</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
